--- a/02_TAK初筛/TAK初筛-117篇.xlsx
+++ b/02_TAK初筛/TAK初筛-117篇.xlsx
@@ -33,1213 +33,1213 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="393">
-  <si>
-    <t>TAK 初筛汇总</t>
-  </si>
-  <si>
-    <t>初筛结果</t>
-  </si>
-  <si>
-    <t>记录数</t>
-  </si>
-  <si>
-    <t>本阶段总记录</t>
-  </si>
-  <si>
-    <t>保留</t>
-  </si>
-  <si>
-    <t>排除</t>
-  </si>
-  <si>
-    <t>筛选范围</t>
-  </si>
-  <si>
-    <t>TAK指标题、摘要和关键词。主要依据标题、摘要及可获得的关键词；个别边界记录结合全文或权威元数据补核。</t>
-  </si>
-  <si>
-    <t>主题要求</t>
-  </si>
-  <si>
-    <t>以蜕变测试、蜕变关系或等价蜕变机制作为核心测试或评价方法；研究对象涉及大语言模型、基础模型或其系统，或使用大语言模型支持蜕变测试。</t>
-  </si>
-  <si>
-    <t>其他纳入条件</t>
-  </si>
-  <si>
-    <t>英文原始研究，包括实证、方法、工具或案例研究；核验日期位于2023-01-01至2026-08-25。</t>
-  </si>
-  <si>
-    <t>排除原则</t>
-  </si>
-  <si>
-    <t>不满足主题、语言、日期或原始研究要求的记录予以排除；综述等二次研究不进入原始研究集。</t>
-  </si>
-  <si>
-    <t>TAK 初筛清单</t>
-  </si>
-  <si>
-    <t>按代表记录的数据库分组</t>
-  </si>
-  <si>
-    <t>主记录 ID</t>
-  </si>
-  <si>
-    <t>论文标题</t>
-  </si>
-  <si>
-    <t>来源数据库</t>
-  </si>
-  <si>
-    <t>初筛结论</t>
-  </si>
-  <si>
-    <t>文献链接</t>
-  </si>
-  <si>
-    <t>MU-0096</t>
-  </si>
-  <si>
-    <t>Combating Missed Recalls in E-commerce Search: A CoT-Prompting Testing Approach</t>
-  </si>
-  <si>
-    <t>ACM DL
+<ns0:sst xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="606" uniqueCount="393">
+  <ns0:si>
+    <ns0:t>TAK 初筛汇总</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>初筛结果</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>记录数</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>本阶段总记录</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>保留</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>排除</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>筛选范围</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TAK指标题、摘要和关键词。主要依据标题、摘要及可获得的关键词；个别边界记录结合全文或权威元数据补核。</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>主题要求</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>以蜕变测试、蜕变关系或等价蜕变机制作为核心测试或评价方法；研究对象涉及大语言模型、基础模型或其系统，或使用大语言模型支持蜕变测试。</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>其他纳入条件</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>英文原始研究，包括实证、方法、工具或案例研究；核验日期位于2023-01-01至2026-08-25。</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>排除原则</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>不满足主题、语言、日期或原始研究要求的记录予以排除；综述等二次研究不进入原始研究集。</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TAK 初筛清单</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>按代表记录的数据库分组</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>主记录 ID</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>论文标题</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>来源数据库</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>初筛结论</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>文献链接</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0096</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Combating Missed Recalls in E-commerce Search: A CoT-Prompting Testing Approach</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ACM DL
 arXiv
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3663529.3663842</t>
-  </si>
-  <si>
-    <t>MU-0106</t>
-  </si>
-  <si>
-    <t>Drowzee: Metamorphic Testing for Fact-Conflicting Hallucination Detection in Large Language Models</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3689776</t>
-  </si>
-  <si>
-    <t>MU-0136</t>
-  </si>
-  <si>
-    <t>Detecting and Reducing the Factual Hallucinations of Large Language Models with Metamorphic Testing</t>
-  </si>
-  <si>
-    <t>ACM DL
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3715784</t>
-  </si>
-  <si>
-    <t>MU-0137</t>
-  </si>
-  <si>
-    <t>Hallucination Detection in Large Language Models with Metamorphic Relations</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3715735</t>
-  </si>
-  <si>
-    <t>MU-0139</t>
-  </si>
-  <si>
-    <t>QTRAN: Extending Metamorphic-Oracle Based Logical Bug Detection Techniques for Multiple-DBMS Dialect Support</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3728908</t>
-  </si>
-  <si>
-    <t>MU-0149</t>
-  </si>
-  <si>
-    <t>ChatGPT Inaccuracy Mitigation during Technical Report Understanding: Are We There Yet?</t>
-  </si>
-  <si>
-    <t>ACM DL
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3663529.3663842</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0106</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Drowzee: Metamorphic Testing for Fact-Conflicting Hallucination Detection in Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3689776</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0136</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Detecting and Reducing the Factual Hallucinations of Large Language Models with Metamorphic Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ACM DL
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3715784</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0137</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hallucination Detection in Large Language Models with Metamorphic Relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3715735</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0139</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>QTRAN: Extending Metamorphic-Oracle Based Logical Bug Detection Techniques for Multiple-DBMS Dialect Support</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3728908</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0149</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ChatGPT Inaccuracy Mitigation during Technical Report Understanding: Are We There Yet?</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ACM DL
 IEEE Xplore
-arXiv</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ICSE55347.2025.00145</t>
-  </si>
-  <si>
-    <t>MU-0151</t>
-  </si>
-  <si>
-    <t>Metamorphic-Based Many-Objective Distillation of LLMs for Code-Related Tasks</t>
-  </si>
-  <si>
-    <t>ACM DL
+arXiv</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ICSE55347.2025.00145</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0151</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic-Based Many-Objective Distillation of LLMs for Code-Related Tasks</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ACM DL
 IEEE Xplore
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ICSE55347.2025.00230</t>
-  </si>
-  <si>
-    <t>MU-0171</t>
-  </si>
-  <si>
-    <t>MTF: an Open-Source Metamorphic Testing Framework for LLM-based systems</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3787120.3787123</t>
-  </si>
-  <si>
-    <t>MU-0193</t>
-  </si>
-  <si>
-    <t>Robust LLM-as-a-Judge Validators for Assessing the Quality of Educational Exams</t>
-  </si>
-  <si>
-    <t>ACM DL</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3748522.3779926</t>
-  </si>
-  <si>
-    <t>MU-0199</t>
-  </si>
-  <si>
-    <t>OBsmith: LLM-Powered JavaScript Obfuscator Testing</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3798204</t>
-  </si>
-  <si>
-    <t>MU-0209</t>
-  </si>
-  <si>
-    <t>How Multi-Modal LLMs Reshape Visual Deep Learning Testing? A Comprehensive Study Through the Lens of Image Mutation</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3815578</t>
-  </si>
-  <si>
-    <t>MU-0221</t>
-  </si>
-  <si>
-    <t>MR-Coupler: Automated Metamorphic Test Generation via Functional Coupling Analysis</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3808213</t>
-  </si>
-  <si>
-    <t>MU-0222</t>
-  </si>
-  <si>
-    <t>Validating LLM-Generated SQL Queries through Metamorphic Prompting</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3797146</t>
-  </si>
-  <si>
-    <t>MU-0227</t>
-  </si>
-  <si>
-    <t>How Robustly Do LLMs Understand Execution Semantics?</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3805760.3814919</t>
-  </si>
-  <si>
-    <t>MU-0251</t>
-  </si>
-  <si>
-    <t>Bias Testing and Mitigation in Black Box LLMs using Metamorphic Relations</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3841176</t>
-  </si>
-  <si>
-    <t>MU-0076</t>
-  </si>
-  <si>
-    <t>Automated Metamorphic-Relation Generation with ChatGPT: An Experience Report</t>
-  </si>
-  <si>
-    <t>IEEE Xplore
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/COMPSAC57700.2023.00275</t>
-  </si>
-  <si>
-    <t>MU-0087</t>
-  </si>
-  <si>
-    <t>Evaluating LLM’s Code Reading Abilities in Big Data Contexts using Metamorphic Testing</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/BigDIA60676.2023.10429345</t>
-  </si>
-  <si>
-    <t>MU-0092</t>
-  </si>
-  <si>
-    <t>MeTMaP: Metamorphic Testing for Detecting False Vector Matching Problems in LLM Augmented Generation</t>
-  </si>
-  <si>
-    <t>ACM DL
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ICSE55347.2025.00230</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0171</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MTF: an Open-Source Metamorphic Testing Framework for LLM-based systems</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3787120.3787123</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0193</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Robust LLM-as-a-Judge Validators for Assessing the Quality of Educational Exams</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ACM DL</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3748522.3779926</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0199</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>OBsmith: LLM-Powered JavaScript Obfuscator Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3798204</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0209</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>How Multi-Modal LLMs Reshape Visual Deep Learning Testing? A Comprehensive Study Through the Lens of Image Mutation</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3815578</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0221</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MR-Coupler: Automated Metamorphic Test Generation via Functional Coupling Analysis</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3808213</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0222</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Validating LLM-Generated SQL Queries through Metamorphic Prompting</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3797146</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0227</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>How Robustly Do LLMs Understand Execution Semantics?</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3805760.3814919</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0251</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bias Testing and Mitigation in Black Box LLMs using Metamorphic Relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3841176</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0076</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Automated Metamorphic-Relation Generation with ChatGPT: An Experience Report</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>IEEE Xplore
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/COMPSAC57700.2023.00275</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0087</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Evaluating LLM’s Code Reading Abilities in Big Data Contexts using Metamorphic Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/BigDIA60676.2023.10429345</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0092</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MeTMaP: Metamorphic Testing for Detecting False Vector Matching Problems in LLM Augmented Generation</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ACM DL
 IEEE Xplore
 arXiv
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1145/3650105.3652297</t>
-  </si>
-  <si>
-    <t>MU-0093</t>
-  </si>
-  <si>
-    <t>METAL: Metamorphic Testing Framework for Analyzing Large-Language Model Qualities</t>
-  </si>
-  <si>
-    <t>IEEE Xplore
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1145/3650105.3652297</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0093</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>METAL: Metamorphic Testing Framework for Analyzing Large-Language Model Qualities</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>IEEE Xplore
 arXiv
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ICST60714.2024.00019</t>
-  </si>
-  <si>
-    <t>MU-0094</t>
-  </si>
-  <si>
-    <t>Detecting Bias in LLMs' Natural Language Inference Using Metamorphic Testing</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/QRS-C63300.2024.00015</t>
-  </si>
-  <si>
-    <t>MU-0095</t>
-  </si>
-  <si>
-    <t>Enabling Effective Metamorphic- Relation Generation by Novice Testers: A Pilot Study</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/COMPSAC61105.2024.00384</t>
-  </si>
-  <si>
-    <t>MU-0099</t>
-  </si>
-  <si>
-    <t>A Symmetric Metamorphic Relations Approach Supporting LLM for Education Technology</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ISET61814.2024.00017</t>
-  </si>
-  <si>
-    <t>MU-0111</t>
-  </si>
-  <si>
-    <t>MR-Adopt: Automatic Deduction of Input Transformation Function for Metamorphic Testing</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/document/10764814/</t>
-  </si>
-  <si>
-    <t>MU-0121</t>
-  </si>
-  <si>
-    <t>Can Large Language Models Discover Metamorphic Relations? A Large-Scale Empirical Study</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/SANER64311.2025.00011</t>
-  </si>
-  <si>
-    <t>MU-0127</t>
-  </si>
-  <si>
-    <t>Semantic-Preserving Transformations as Mutation Operators: A Study on Their Effectiveness in Defect Detection</t>
-  </si>
-  <si>
-    <t>IEEE Xplore
-arXiv</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ICSTW64639.2025.10962512</t>
-  </si>
-  <si>
-    <t>MU-0132</t>
-  </si>
-  <si>
-    <t>Metamon: Finding Inconsistencies between Program Documentation and Behavior using Metamorphic LLM Queries</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/LLM4Code66737.2025.00020</t>
-  </si>
-  <si>
-    <t>MU-0134</t>
-  </si>
-  <si>
-    <t>Metamorphic Testing for Fairness Evaluation in Large Language Models: Identifying Intersectional Bias in LLaMA and GPT</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/SERA65747.2025.11154488</t>
-  </si>
-  <si>
-    <t>MU-0145</t>
-  </si>
-  <si>
-    <t>Efficient Fairness Testing in Large Language Models: Prioritizing Metamorphic Relations for Bias Detection</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/AITest66680.2025.00031</t>
-  </si>
-  <si>
-    <t>MU-0146</t>
-  </si>
-  <si>
-    <t>GenFair: Systematic Test Generation for Fairness Fault Detection in Large Language Models</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/AITest66680.2025.00030</t>
-  </si>
-  <si>
-    <t>MU-0147</t>
-  </si>
-  <si>
-    <t>A Pilot Study of Probing Before Trusting Large Language Models in Self-Learning</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ISET65607.2025.00046</t>
-  </si>
-  <si>
-    <t>MU-0148</t>
-  </si>
-  <si>
-    <t>Metamorphic Testing of Large Language Models for Natural Language Processing</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ICSME64153.2025.00025</t>
-  </si>
-  <si>
-    <t>MU-0150</t>
-  </si>
-  <si>
-    <t>LLM-assisted Metamorphic Testing of Embedded Graphics Libraries</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/FDL68117.2025.11165405</t>
-  </si>
-  <si>
-    <t>MU-0161</t>
-  </si>
-  <si>
-    <t>Chrysalis: A Lightweight Logging and Replay Framework for Metamorphic Testing in Python</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ASE63991.2025.00371</t>
-  </si>
-  <si>
-    <t>MU-0162</t>
-  </si>
-  <si>
-    <t>LLMorph: Automated Metamorphic Testing of Large Language Models</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ASE63991.2025.00385</t>
-  </si>
-  <si>
-    <t>MU-0163</t>
-  </si>
-  <si>
-    <t>LLMs in Debate: Does Arguing Make Them Better at Detecting Metamorphic Relations?</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ASEW67777.2025.00019</t>
-  </si>
-  <si>
-    <t>MU-0169</t>
-  </si>
-  <si>
-    <t>PromptOps: Automated Tool for Testing Trustworthiness of LLMs</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/APSEC66846.2025.00117</t>
-  </si>
-  <si>
-    <t>MU-0170</t>
-  </si>
-  <si>
-    <t>SVPrompt-MR: An LLM-Based Metamorphic Relation Identification Method with Self-Verification Mechanism</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/APSEC66846.2025.00055</t>
-  </si>
-  <si>
-    <t>MU-0172</t>
-  </si>
-  <si>
-    <t>TEMPLEs: Teacher Evaluation using Metamorphic-mediated Personality-aware LLM Evaluators</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/TALE66047.2025.11346704</t>
-  </si>
-  <si>
-    <t>MU-0175</t>
-  </si>
-  <si>
-    <t>Metamorphic Testing for Semantic Invariance in Large Language Models</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/ACCESS.2025.3646270</t>
-  </si>
-  <si>
-    <t>MU-0182</t>
-  </si>
-  <si>
-    <t>Quantitative Reflection for Mental State Analysis via Aspect Sentiment Triplet Extraction</t>
-  </si>
-  <si>
-    <t>IEEE Xplore</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/TAFFC.2026.3663142</t>
-  </si>
-  <si>
-    <t>MU-0217</t>
-  </si>
-  <si>
-    <t>MORTAR: Multi-turn Metamorphic Testing for LLM-based Dialogue Systems</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/TSE.2026.3701230</t>
-  </si>
-  <si>
-    <t>MU-0228</t>
-  </si>
-  <si>
-    <t>Multi-Agent LLM-Based Metamorphic Testing for REST APIs</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/COMPSAC69091.2026.00043</t>
-  </si>
-  <si>
-    <t>MU-0229</t>
-  </si>
-  <si>
-    <t>Multi-Agent Specification-Based Metamorphic Testing of FMU-Based Simulations</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/COMPSAC69091.2026.00424</t>
-  </si>
-  <si>
-    <t>MU-0230</t>
-  </si>
-  <si>
-    <t>Temporal Metamorphic Testing for RAG-Based LLMs under Evolving Knowledge</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/COMPSAC69091.2026.00368</t>
-  </si>
-  <si>
-    <t>MU-0231</t>
-  </si>
-  <si>
-    <t>Toward Standardized Evaluation of Metamorphic Relations: A Structured Rubric and Human-LLM Comparison</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/COMPSAC69091.2026.00027</t>
-  </si>
-  <si>
-    <t>MU-0238</t>
-  </si>
-  <si>
-    <t>LLM-Based Automatic Metamorphic Test Case Generation for LLM Fairness Testing</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/AITest70988.2026.00012</t>
-  </si>
-  <si>
-    <t>MU-0239</t>
-  </si>
-  <si>
-    <t>Metamorphic Testing of Multi-Agent LLM Systems: A Trace-Based Behavioral Oracle Framework</t>
-  </si>
-  <si>
-    <t>DOI: 10.1109/AITest70988.2026.00036</t>
-  </si>
-  <si>
-    <t>MU-0116</t>
-  </si>
-  <si>
-    <t>Effectiveness of symmetric metamorphic relations on validating the stability of code generation LLM</t>
-  </si>
-  <si>
-    <t>ScienceDirect
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.jss.2024.112330</t>
-  </si>
-  <si>
-    <t>MU-0128</t>
-  </si>
-  <si>
-    <t>Metamorphic Testing for Robustness and Fairness Evaluation of LLM-based Automated ICD Coding Applications</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.smhl.2025.100564</t>
-  </si>
-  <si>
-    <t>MU-0143</t>
-  </si>
-  <si>
-    <t>Enhancing autonomous driving simulations: A hybrid metamorphic testing framework with metamorphic relations generated by GPT</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.infsof.2025.107828</t>
-  </si>
-  <si>
-    <t>MU-0164</t>
-  </si>
-  <si>
-    <t>Automated end-to-end testing for conversational agents</t>
-  </si>
-  <si>
-    <t>ScienceDirect</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.jss.2025.112685</t>
-  </si>
-  <si>
-    <t>MU-0184</t>
-  </si>
-  <si>
-    <t>Meta-Fair: AI-assisted fairness testing of large language models</t>
-  </si>
-  <si>
-    <t>IEEE Xplore
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ICST60714.2024.00019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0094</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Detecting Bias in LLMs' Natural Language Inference Using Metamorphic Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/QRS-C63300.2024.00015</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0095</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Enabling Effective Metamorphic- Relation Generation by Novice Testers: A Pilot Study</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/COMPSAC61105.2024.00384</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0099</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>A Symmetric Metamorphic Relations Approach Supporting LLM for Education Technology</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ISET61814.2024.00017</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0111</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MR-Adopt: Automatic Deduction of Input Transformation Function for Metamorphic Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://ieeexplore.ieee.org/document/10764814/</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0121</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Can Large Language Models Discover Metamorphic Relations? A Large-Scale Empirical Study</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/SANER64311.2025.00011</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0127</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Semantic-Preserving Transformations as Mutation Operators: A Study on Their Effectiveness in Defect Detection</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>IEEE Xplore
+arXiv</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ICSTW64639.2025.10962512</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0132</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamon: Finding Inconsistencies between Program Documentation and Behavior using Metamorphic LLM Queries</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/LLM4Code66737.2025.00020</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0134</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Testing for Fairness Evaluation in Large Language Models: Identifying Intersectional Bias in LLaMA and GPT</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/SERA65747.2025.11154488</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0145</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Efficient Fairness Testing in Large Language Models: Prioritizing Metamorphic Relations for Bias Detection</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/AITest66680.2025.00031</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0146</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>GenFair: Systematic Test Generation for Fairness Fault Detection in Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/AITest66680.2025.00030</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0147</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>A Pilot Study of Probing Before Trusting Large Language Models in Self-Learning</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ISET65607.2025.00046</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0148</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Testing of Large Language Models for Natural Language Processing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ICSME64153.2025.00025</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0150</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LLM-assisted Metamorphic Testing of Embedded Graphics Libraries</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/FDL68117.2025.11165405</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0161</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Chrysalis: A Lightweight Logging and Replay Framework for Metamorphic Testing in Python</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ASE63991.2025.00371</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0162</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LLMorph: Automated Metamorphic Testing of Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ASE63991.2025.00385</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0163</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LLMs in Debate: Does Arguing Make Them Better at Detecting Metamorphic Relations?</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ASEW67777.2025.00019</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0169</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>PromptOps: Automated Tool for Testing Trustworthiness of LLMs</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/APSEC66846.2025.00117</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0170</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SVPrompt-MR: An LLM-Based Metamorphic Relation Identification Method with Self-Verification Mechanism</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/APSEC66846.2025.00055</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0172</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>TEMPLEs: Teacher Evaluation using Metamorphic-mediated Personality-aware LLM Evaluators</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/TALE66047.2025.11346704</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0175</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Testing for Semantic Invariance in Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/ACCESS.2025.3646270</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0182</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Quantitative Reflection for Mental State Analysis via Aspect Sentiment Triplet Extraction</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>IEEE Xplore</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/TAFFC.2026.3663142</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0217</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MORTAR: Multi-turn Metamorphic Testing for LLM-based Dialogue Systems</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/TSE.2026.3701230</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0228</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Multi-Agent LLM-Based Metamorphic Testing for REST APIs</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/COMPSAC69091.2026.00043</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0229</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Multi-Agent Specification-Based Metamorphic Testing of FMU-Based Simulations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/COMPSAC69091.2026.00424</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0230</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Temporal Metamorphic Testing for RAG-Based LLMs under Evolving Knowledge</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/COMPSAC69091.2026.00368</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0231</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Toward Standardized Evaluation of Metamorphic Relations: A Structured Rubric and Human-LLM Comparison</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/COMPSAC69091.2026.00027</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0238</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LLM-Based Automatic Metamorphic Test Case Generation for LLM Fairness Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/AITest70988.2026.00012</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0239</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Testing of Multi-Agent LLM Systems: A Trace-Based Behavioral Oracle Framework</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1109/AITest70988.2026.00036</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0116</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Effectiveness of symmetric metamorphic relations on validating the stability of code generation LLM</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ScienceDirect
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.jss.2024.112330</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0128</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Testing for Robustness and Fairness Evaluation of LLM-based Automated ICD Coding Applications</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.smhl.2025.100564</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0143</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Enhancing autonomous driving simulations: A hybrid metamorphic testing framework with metamorphic relations generated by GPT</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.infsof.2025.107828</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0164</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Automated end-to-end testing for conversational agents</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ScienceDirect</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.jss.2025.112685</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0184</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Meta-Fair: AI-assisted fairness testing of large language models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>IEEE Xplore
 ScienceDirect
 arXiv
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.infsof.2026.108075</t>
-  </si>
-  <si>
-    <t>MU-0200</t>
-  </si>
-  <si>
-    <t>Towards metamorphic testing with LLM-based workflows: Metamorphic relation inference and follow-up test case generation</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.infsof.2026.108150</t>
-  </si>
-  <si>
-    <t>MU-0210</t>
-  </si>
-  <si>
-    <t>A metamorphic testing perspective on knowledge distillation for language models of code: Does the student deeply mimic the teacher?</t>
-  </si>
-  <si>
-    <t>ScienceDirect
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.infsof.2026.108075</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0200</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Towards metamorphic testing with LLM-based workflows: Metamorphic relation inference and follow-up test case generation</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.infsof.2026.108150</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0210</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>A metamorphic testing perspective on knowledge distillation for language models of code: Does the student deeply mimic the teacher?</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ScienceDirect
 arXiv
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.jss.2026.112952</t>
-  </si>
-  <si>
-    <t>MU-0214</t>
-  </si>
-  <si>
-    <t>HalluTrigger: Triggering input-conflicting hallucinations in large language models with semantic-guided metamorphic relations</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.eswa.2026.132644</t>
-  </si>
-  <si>
-    <t>MU-0216</t>
-  </si>
-  <si>
-    <t>LGMT: Logic-Grounded Metamorphic Testing for evaluating the reasoning reliability of LLMs</t>
-  </si>
-  <si>
-    <t>DOI: 10.1016/j.knosys.2026.116324</t>
-  </si>
-  <si>
-    <t>MU-0077</t>
-  </si>
-  <si>
-    <t>Variable Discovery with Large Language Models for Metamorphic Testing of Scientific Software</t>
-  </si>
-  <si>
-    <t>IEEE Xplore
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.jss.2026.112952</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0214</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>HalluTrigger: Triggering input-conflicting hallucinations in large language models with semantic-guided metamorphic relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.eswa.2026.132644</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0216</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LGMT: Logic-Grounded Metamorphic Testing for evaluating the reasoning reliability of LLMs</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1016/j.knosys.2026.116324</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0077</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Variable Discovery with Large Language Models for Metamorphic Testing of Scientific Software</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>IEEE Xplore
 SpringerLink
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1007/978-3-031-35995-8_23</t>
-  </si>
-  <si>
-    <t>MU-0105</t>
-  </si>
-  <si>
-    <t>Towards Generating Executable Metamorphic Relations Using Large Language Models</t>
-  </si>
-  <si>
-    <t>SpringerLink
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1007/978-3-031-35995-8_23</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0105</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Towards Generating Executable Metamorphic Relations Using Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SpringerLink
 arXiv
-Google Scholar</t>
-  </si>
-  <si>
-    <t>DOI: 10.1007/978-3-031-70245-7_9</t>
-  </si>
-  <si>
-    <t>MU-0140</t>
-  </si>
-  <si>
-    <t>Test It Before You Trust It: Applying Software Testing for Trustworthy In-Context Learning</t>
-  </si>
-  <si>
-    <t>DOI: 10.1007/978-3-031-97141-9_17</t>
-  </si>
-  <si>
-    <t>MU-0165</t>
-  </si>
-  <si>
-    <t>LLMTest: Combining Symbolic Execution and LLM Capabilities for Commutativity Test of Reduce Functions</t>
-  </si>
-  <si>
-    <t>SpringerLink</t>
-  </si>
-  <si>
-    <t>DOI: 10.1007/978-981-95-4990-0_9</t>
-  </si>
-  <si>
-    <t>MU-0206</t>
-  </si>
-  <si>
-    <t>Using large language models to test voice user interfaces</t>
-  </si>
-  <si>
-    <t>DOI: 10.1007/s10664-026-10859-7</t>
-  </si>
-  <si>
-    <t>MU-0253</t>
-  </si>
-  <si>
-    <t>Foundation models as oracles for refactoring correctness detection</t>
-  </si>
-  <si>
-    <t>SpringerLink
-arXiv</t>
-  </si>
-  <si>
-    <t>DOI: 10.1007/s10664-026-10951-y</t>
-  </si>
-  <si>
-    <t>MU-0084</t>
-  </si>
-  <si>
-    <t>On the Potential and Limitations of Few-Shot In-Context Learning to Generate Metamorphic Specifications for Tax Preparation Software</t>
-  </si>
-  <si>
-    <t>arXiv
-Google Scholar</t>
-  </si>
-  <si>
-    <t>arXiv:2311.11979</t>
-  </si>
-  <si>
-    <t>MU-0086</t>
-  </si>
-  <si>
-    <t>VRPTEST: Evaluating Visual Referring Prompting in Large Multimodal Models</t>
-  </si>
-  <si>
-    <t>arXiv</t>
-  </si>
-  <si>
-    <t>arXiv:2312.04087</t>
-  </si>
-  <si>
-    <t>MU-0089</t>
-  </si>
-  <si>
-    <t>An Empirical Study on Large Language Models in Accuracy and Robustness under Chinese Industrial Scenarios</t>
-  </si>
-  <si>
-    <t>arXiv:2402.01723</t>
-  </si>
-  <si>
-    <t>MU-0107</t>
-  </si>
-  <si>
-    <t>Exploring and Lifting the Robustness of LLM-powered Automated Program Repair with Metamorphic Testing</t>
-  </si>
-  <si>
-    <t>arXiv:2410.07516</t>
-  </si>
-  <si>
-    <t>MU-0113</t>
-  </si>
-  <si>
-    <t>Metamorphic Evaluation of ChatGPT as a Recommender System</t>
-  </si>
-  <si>
-    <t>arXiv:2411.12121</t>
-  </si>
-  <si>
-    <t>MU-0117</t>
-  </si>
-  <si>
-    <t>PCS: Perceived Confidence Scoring of Black Box LLMs with Metamorphic Relations</t>
-  </si>
-  <si>
-    <t>arXiv:2502.07186</t>
-  </si>
-  <si>
-    <t>MU-0118</t>
-  </si>
-  <si>
-    <t>Detecting LLM Fact-conflicting Hallucinations Enhanced by Temporal-logic-based Reasoning</t>
-  </si>
-  <si>
-    <t>arXiv:2502.13416</t>
-  </si>
-  <si>
-    <t>MU-0122</t>
-  </si>
-  <si>
-    <t>HInter: Exposing Hidden Intersectional Bias in Large Language Models</t>
-  </si>
-  <si>
-    <t>arXiv:2503.11962</t>
-  </si>
-  <si>
-    <t>MU-0123</t>
-  </si>
-  <si>
-    <t>Automated Harmfulness Testing for Code Large Language Models</t>
-  </si>
-  <si>
-    <t>arXiv:2503.16740</t>
-  </si>
-  <si>
-    <t>MU-0126</t>
-  </si>
-  <si>
-    <t>Integrating Artificial Intelligence with Human Expertise: An In-depth Analysis of ChatGPT''s Capabilities in Generating Metamorphic Relations</t>
-  </si>
-  <si>
-    <t>arXiv:2503.22141</t>
-  </si>
-  <si>
-    <t>MU-0141</t>
-  </si>
-  <si>
-    <t>ASSURE: Metamorphic Testing for AI-powered Browser Extensions</t>
-  </si>
-  <si>
-    <t>arXiv:2507.05307</t>
-  </si>
-  <si>
-    <t>MU-0142</t>
-  </si>
-  <si>
-    <t>Search-based Selection of Metamorphic Relations for Optimized Robustness Testing of Large Language Models</t>
-  </si>
-  <si>
-    <t>arXiv:2507.05565</t>
-  </si>
-  <si>
-    <t>MU-0144</t>
-  </si>
-  <si>
-    <t>StaAgent: An Agentic Framework for Testing Static Analyzers</t>
-  </si>
-  <si>
-    <t>arXiv:2507.15892</t>
-  </si>
-  <si>
-    <t>MU-0152</t>
-  </si>
-  <si>
-    <t>MetaRAG: Metamorphic Testing for Hallucination Detection in RAG Systems</t>
-  </si>
-  <si>
-    <t>arXiv:2509.09360</t>
-  </si>
-  <si>
-    <t>MU-0153</t>
-  </si>
-  <si>
-    <t>An LLM Agentic Approach for Legal-Critical Software: A Case Study for Tax Prep Software</t>
-  </si>
-  <si>
-    <t>arXiv:2509.13471</t>
-  </si>
-  <si>
-    <t>MU-0154</t>
-  </si>
-  <si>
-    <t>Fairness Testing in Retrieval-Augmented Generation: How Small Perturbations Reveal Bias in Small Language Models</t>
-  </si>
-  <si>
-    <t>arXiv:2509.26584</t>
-  </si>
-  <si>
-    <t>MU-0156</t>
-  </si>
-  <si>
-    <t>AutoMT: A Multi-Agent LLM Framework for Automated Metamorphic Testing of Autonomous Driving Systems</t>
-  </si>
-  <si>
-    <t>arXiv:2510.19438</t>
-  </si>
-  <si>
-    <t>MU-0159</t>
-  </si>
-  <si>
-    <t>Testing Question Answering Software with Context-Driven Question Generation</t>
-  </si>
-  <si>
-    <t>arXiv:2511.07924</t>
-  </si>
-  <si>
-    <t>MU-0160</t>
-  </si>
-  <si>
-    <t>Reducing Hallucinations in LLM-Generated Code via Semantic Triangulation</t>
-  </si>
-  <si>
-    <t>arXiv:2511.12288</t>
-  </si>
-  <si>
-    <t>MU-0167</t>
-  </si>
-  <si>
-    <t>LLM Assisted Coding with Metamorphic Specification Mutation Agent</t>
-  </si>
-  <si>
-    <t>arXiv:2511.18249</t>
-  </si>
-  <si>
-    <t>MU-0174</t>
-  </si>
-  <si>
-    <t>Toward Systematic Counterfactual Fairness Evaluation of Large Language Models: The CAFFE Framework</t>
-  </si>
-  <si>
-    <t>arXiv:2512.16816</t>
-  </si>
-  <si>
-    <t>MU-0177</t>
-  </si>
-  <si>
-    <t>Hallucination Detection for LLM-based Text-to-SQL Generation via Two-Stage Metamorphic Testing</t>
-  </si>
-  <si>
-    <t>arXiv:2512.22250</t>
-  </si>
-  <si>
-    <t>MU-0179</t>
-  </si>
-  <si>
-    <t>ReliabilityBench: Evaluating LLM Agent Reliability Under Production-Like Stress Conditions</t>
-  </si>
-  <si>
-    <t>arXiv:2601.06112</t>
-  </si>
-  <si>
-    <t>MU-0186</t>
-  </si>
-  <si>
-    <t>AgentAssay: Token-Efficient Regression Testing for Non-Deterministic AI Agent Workflows</t>
-  </si>
-  <si>
-    <t>arXiv:2603.02601</t>
-  </si>
-  <si>
-    <t>MU-0188</t>
-  </si>
-  <si>
-    <t>Semantic Invariance in Agentic AI</t>
-  </si>
-  <si>
-    <t>arXiv:2603.13173</t>
-  </si>
-  <si>
-    <t>MU-0194</t>
-  </si>
-  <si>
-    <t>Can Language Models Pass Software Testing Certification Exams? a case study</t>
-  </si>
-  <si>
-    <t>arXiv:2603.23142</t>
-  </si>
-  <si>
-    <t>MU-0204</t>
-  </si>
-  <si>
-    <t>A Metamorphic Testing Approach to Diagnosing Memorization in LLM-Based Program Repair</t>
-  </si>
-  <si>
-    <t>arXiv:2604.21579</t>
-  </si>
-  <si>
-    <t>MU-0211</t>
-  </si>
-  <si>
-    <t>A semantic mutation metric for metamorphic relation adequacy in scientific computing programs</t>
-  </si>
-  <si>
-    <t>arXiv:2605.17437</t>
-  </si>
-  <si>
-    <t>MU-0215</t>
-  </si>
-  <si>
-    <t>MetaRA: Metamorphic Robustness Assessment for Multimodal Large Language Model-based Visual Question Answering Systems</t>
-  </si>
-  <si>
-    <t>arXiv:2605.19307</t>
-  </si>
-  <si>
-    <t>MU-0219</t>
-  </si>
-  <si>
-    <t>Investigating Metamorphic Fuzz Oracle Enhancement via Large Language Models</t>
-  </si>
-  <si>
-    <t>arXiv:2606.14164</t>
-  </si>
-  <si>
-    <t>MU-0226</t>
-  </si>
-  <si>
-    <t>NormWorlds-CF: Solver-Verified Counterfactual Normative Reasoning with Metamorphic-Relation GRPO</t>
-  </si>
-  <si>
-    <t>arXiv:2607.03957</t>
-  </si>
-  <si>
-    <t>MU-0233</t>
-  </si>
-  <si>
-    <t>Cross-Cutting Security Analysis of LLM-Generated Code via Metamorphic Testing and Association Rule Mining</t>
-  </si>
-  <si>
-    <t>arXiv:2607.12089</t>
-  </si>
-  <si>
-    <t>MU-0237</t>
-  </si>
-  <si>
-    <t>Chiral Analysis of Smart Contracts: Detecting Vulnerabilities from Relational Inconsistencies Across Business Paths</t>
-  </si>
-  <si>
-    <t>arXiv:2607.17987</t>
-  </si>
-  <si>
-    <t>MU-0240</t>
-  </si>
-  <si>
-    <t>When Knowledge Changes: Metamorphic Testing of RAG Systems with Mutations</t>
-  </si>
-  <si>
-    <t>arXiv:2607.26843</t>
-  </si>
-  <si>
-    <t>MU-0241</t>
-  </si>
-  <si>
-    <t>Not as Sweet by Another Name: An Empirical Study of Format Robustness in LLM Document Workflows</t>
-  </si>
-  <si>
-    <t>arXiv:2607.27648</t>
-  </si>
-  <si>
-    <t>MU-0242</t>
-  </si>
-  <si>
-    <t>Repository-Aware Metamorphic Relation Generation for Augmented Reality Applications using Large Language Models</t>
-  </si>
-  <si>
-    <t>arXiv:2607.28775</t>
-  </si>
-  <si>
-    <t>MU-0244</t>
-  </si>
-  <si>
-    <t>Assessing Behavioral Validation in UI Component Test Suites Using Inferred Metamorphic Relations</t>
-  </si>
-  <si>
-    <t>arXiv:2608.03337</t>
-  </si>
-  <si>
-    <t>MU-0246</t>
-  </si>
-  <si>
-    <t>Explanation-Guided Metamorphic Testing of Specialized Language Models: An Empirical Study</t>
-  </si>
-  <si>
-    <t>arXiv:2608.07076</t>
-  </si>
-  <si>
-    <t>MU-0080</t>
-  </si>
-  <si>
-    <t>LLM-Assisted Test Generation for Validating OpenACC Compiler Implementations</t>
-  </si>
-  <si>
-    <t>Google Scholar</t>
-  </si>
-  <si>
-    <t>查看文献（www.researchgate.net）</t>
-  </si>
-  <si>
-    <t>MU-0082</t>
-  </si>
-  <si>
-    <t>Can ChatGPT advance software testing intelligence? An experience report on metamorphic testing</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2310.19204</t>
-  </si>
-  <si>
-    <t>MU-0091</t>
-  </si>
-  <si>
-    <t>Research on trustworthy Software Testing Techniques Based on Large Models</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/abstract/document/10562113/</t>
-  </si>
-  <si>
-    <t>MU-0108</t>
-  </si>
-  <si>
-    <t>Validating pretrained language models for content quality classification with semantic-preserving metamorphic relations</t>
-  </si>
-  <si>
-    <t>https://www.sciencedirect.com/science/article/pii/S2949719124000621</t>
-  </si>
-  <si>
-    <t>MU-0110</t>
-  </si>
-  <si>
-    <t>Evaluating terminology translation in machine translation systems via metamorphic testing</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/abs/10.1145/3691620.3695069</t>
-  </si>
-  <si>
-    <t>MU-0129</t>
-  </si>
-  <si>
-    <t>Bias unveiled: Investigating social bias in LLM-generated code</t>
-  </si>
-  <si>
-    <t>https://ojs.aaai.org/index.php/AAAI/article/view/34961</t>
-  </si>
-  <si>
-    <t>MU-0173</t>
-  </si>
-  <si>
-    <t>Metamorphic testing of large language model question answering systems</t>
-  </si>
-  <si>
-    <t>查看文献（www.spiedigitallibrary.org）</t>
-  </si>
-  <si>
-    <t>MU-0176</t>
-  </si>
-  <si>
-    <t>Detecting Non-Optimal Decisions of Embodied Agents via Diversity-Guided Metamorphic Testing</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2512.20083</t>
-  </si>
-  <si>
-    <t>MU-0198</t>
-  </si>
-  <si>
-    <t>MetaSpace: Metamorphic Testing for Spatial Cognition in Embodied Agents</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/abs/10.1145/3798212</t>
-  </si>
-  <si>
-    <t>MU-0213</t>
-  </si>
-  <si>
-    <t>Metamorphic Testing of Vision–Language Action–Enabled Robots</t>
-  </si>
-  <si>
-    <t>https://ieeexplore.ieee.org/abstract/document/11600516/</t>
-  </si>
-  <si>
-    <t>MU-0220</t>
-  </si>
-  <si>
-    <t>Beyond the Visible: Transforming AR/VR Software Engineering Through Empirical Discovery, Metamorphic Testing, and Multi-Agent Intelligence</t>
-  </si>
-  <si>
-    <t>https://vtechworks.lib.vt.edu/items/054d386b-8c5f-4c64-a2ca-a4a77870444a</t>
-  </si>
-  <si>
-    <t>MU-0223</t>
-  </si>
-  <si>
-    <t>SGVEF-LOOP: Coverage-Guided Progressive Topological Exploration and Fact-Grounded Metamorphic Evaluation for MCP Agents</t>
-  </si>
-  <si>
-    <t>https://aclanthology.org/2026.acl-long.1224/</t>
-  </si>
-  <si>
-    <t>MU-0225</t>
-  </si>
-  <si>
-    <t>Kaizen: Metamorphic Fuzzing and Differential Testing for LLM-Translated HPC Applications</t>
-  </si>
-  <si>
-    <t>https://arxiv.org/abs/2607.04058</t>
-  </si>
-  <si>
-    <t>MU-0232</t>
-  </si>
-  <si>
-    <t>Automatic Validation of LLM-Generated Code with Prompt Paraphrasing</t>
-  </si>
-  <si>
-    <t>https://dl.acm.org/doi/abs/10.1145/3786582.3786809</t>
-  </si>
-  <si>
-    <t>MU-0245</t>
-  </si>
-  <si>
-    <t>Metamorphic Fairness Testing of Retrieval-Augmented Generation: Diagnosing Retriever Bias and Evaluating Graph-based Mitigation</t>
-  </si>
-  <si>
-    <t>https://journals-sol.sbc.org.br/index.php/jserd/article/view/7713</t>
-  </si>
-  <si>
-    <t>MU-0247</t>
-  </si>
-  <si>
-    <t>Testing JSON Schema Instruction Artifacts: Distributional Robustness under Validation-Equivalent Serialization and JSON Mode</t>
-  </si>
-  <si>
-    <t>https://www.researchsquare.com/article/rs-10610100/latest</t>
-  </si>
-  <si>
-    <t>MU-0249</t>
-  </si>
-  <si>
-    <t>Uncovering Discriminatory Behavior in LLM-Based CV Screening Systems with Composite Statistical Metamorphic Relations</t>
-  </si>
-  <si>
-    <t>https://ijcai-preprints.s3.us-west-1.amazonaws.com/2026/HC39.pdf</t>
-  </si>
-</sst>
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1007/978-3-031-70245-7_9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0140</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Test It Before You Trust It: Applying Software Testing for Trustworthy In-Context Learning</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1007/978-3-031-97141-9_17</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0165</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LLMTest: Combining Symbolic Execution and LLM Capabilities for Commutativity Test of Reduce Functions</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SpringerLink</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1007/978-981-95-4990-0_9</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0206</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Using large language models to test voice user interfaces</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1007/s10664-026-10859-7</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0253</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Foundation models as oracles for refactoring correctness detection</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SpringerLink
+arXiv</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>DOI: 10.1007/s10664-026-10951-y</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0084</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>On the Potential and Limitations of Few-Shot In-Context Learning to Generate Metamorphic Specifications for Tax Preparation Software</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv
+Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2311.11979</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0086</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>VRPTEST: Evaluating Visual Referring Prompting in Large Multimodal Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2312.04087</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0089</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>An Empirical Study on Large Language Models in Accuracy and Robustness under Chinese Industrial Scenarios</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2402.01723</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0107</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Exploring and Lifting the Robustness of LLM-powered Automated Program Repair with Metamorphic Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2410.07516</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0113</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Evaluation of ChatGPT as a Recommender System</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2411.12121</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0117</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>PCS: Perceived Confidence Scoring of Black Box LLMs with Metamorphic Relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2502.07186</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0118</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Detecting LLM Fact-conflicting Hallucinations Enhanced by Temporal-logic-based Reasoning</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2502.13416</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0122</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>HInter: Exposing Hidden Intersectional Bias in Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2503.11962</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0123</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Automated Harmfulness Testing for Code Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2503.16740</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0126</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Integrating Artificial Intelligence with Human Expertise: An In-depth Analysis of ChatGPT''s Capabilities in Generating Metamorphic Relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2503.22141</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0141</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ASSURE: Metamorphic Testing for AI-powered Browser Extensions</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2507.05307</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0142</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Search-based Selection of Metamorphic Relations for Optimized Robustness Testing of Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2507.05565</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0144</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>StaAgent: An Agentic Framework for Testing Static Analyzers</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2507.15892</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0152</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MetaRAG: Metamorphic Testing for Hallucination Detection in RAG Systems</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2509.09360</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0153</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>An LLM Agentic Approach for Legal-Critical Software: A Case Study for Tax Prep Software</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2509.13471</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0154</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Fairness Testing in Retrieval-Augmented Generation: How Small Perturbations Reveal Bias in Small Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2509.26584</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0156</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>AutoMT: A Multi-Agent LLM Framework for Automated Metamorphic Testing of Autonomous Driving Systems</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2510.19438</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0159</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Testing Question Answering Software with Context-Driven Question Generation</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2511.07924</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0160</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Reducing Hallucinations in LLM-Generated Code via Semantic Triangulation</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2511.12288</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0167</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LLM Assisted Coding with Metamorphic Specification Mutation Agent</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2511.18249</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0174</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Toward Systematic Counterfactual Fairness Evaluation of Large Language Models: The CAFFE Framework</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2512.16816</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0177</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Hallucination Detection for LLM-based Text-to-SQL Generation via Two-Stage Metamorphic Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2512.22250</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0179</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>ReliabilityBench: Evaluating LLM Agent Reliability Under Production-Like Stress Conditions</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2601.06112</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0186</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>AgentAssay: Token-Efficient Regression Testing for Non-Deterministic AI Agent Workflows</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2603.02601</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0188</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Semantic Invariance in Agentic AI</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2603.13173</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0194</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Can Language Models Pass Software Testing Certification Exams? a case study</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2603.23142</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0204</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>A Metamorphic Testing Approach to Diagnosing Memorization in LLM-Based Program Repair</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2604.21579</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0211</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>A semantic mutation metric for metamorphic relation adequacy in scientific computing programs</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2605.17437</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0215</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MetaRA: Metamorphic Robustness Assessment for Multimodal Large Language Model-based Visual Question Answering Systems</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2605.19307</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0219</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Investigating Metamorphic Fuzz Oracle Enhancement via Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2606.14164</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0226</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>NormWorlds-CF: Solver-Verified Counterfactual Normative Reasoning with Metamorphic-Relation GRPO</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2607.03957</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0233</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Cross-Cutting Security Analysis of LLM-Generated Code via Metamorphic Testing and Association Rule Mining</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2607.12089</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0237</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Chiral Analysis of Smart Contracts: Detecting Vulnerabilities from Relational Inconsistencies Across Business Paths</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2607.17987</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0240</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>When Knowledge Changes: Metamorphic Testing of RAG Systems with Mutations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2607.26843</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0241</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Not as Sweet by Another Name: An Empirical Study of Format Robustness in LLM Document Workflows</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2607.27648</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0242</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Repository-Aware Metamorphic Relation Generation for Augmented Reality Applications using Large Language Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2607.28775</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0244</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Assessing Behavioral Validation in UI Component Test Suites Using Inferred Metamorphic Relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2608.03337</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0246</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Explanation-Guided Metamorphic Testing of Specialized Language Models: An Empirical Study</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>arXiv:2608.07076</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0080</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>LLM-Assisted Test Generation for Validating OpenACC Compiler Implementations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Google Scholar</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>查看文献（www.researchgate.net）</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0082</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Can ChatGPT advance software testing intelligence? An experience report on metamorphic testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://arxiv.org/abs/2310.19204</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0091</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Research on trustworthy Software Testing Techniques Based on Large Models</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://ieeexplore.ieee.org/abstract/document/10562113/</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0108</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Validating pretrained language models for content quality classification with semantic-preserving metamorphic relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://www.sciencedirect.com/science/article/pii/S2949719124000621</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0110</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Evaluating terminology translation in machine translation systems via metamorphic testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://dl.acm.org/doi/abs/10.1145/3691620.3695069</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0129</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Bias unveiled: Investigating social bias in LLM-generated code</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://ojs.aaai.org/index.php/AAAI/article/view/34961</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0173</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic testing of large language model question answering systems</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>查看文献（www.spiedigitallibrary.org）</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0176</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Detecting Non-Optimal Decisions of Embodied Agents via Diversity-Guided Metamorphic Testing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://arxiv.org/abs/2512.20083</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0198</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MetaSpace: Metamorphic Testing for Spatial Cognition in Embodied Agents</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://dl.acm.org/doi/abs/10.1145/3798212</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0213</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Testing of Vision–Language Action–Enabled Robots</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://ieeexplore.ieee.org/abstract/document/11600516/</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0220</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Beyond the Visible: Transforming AR/VR Software Engineering Through Empirical Discovery, Metamorphic Testing, and Multi-Agent Intelligence</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://vtechworks.lib.vt.edu/items/054d386b-8c5f-4c64-a2ca-a4a77870444a</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0223</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>SGVEF-LOOP: Coverage-Guided Progressive Topological Exploration and Fact-Grounded Metamorphic Evaluation for MCP Agents</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://aclanthology.org/2026.acl-long.1224/</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0225</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Kaizen: Metamorphic Fuzzing and Differential Testing for LLM-Translated HPC Applications</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://arxiv.org/abs/2607.04058</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0232</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Automatic Validation of LLM-Generated Code with Prompt Paraphrasing</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://dl.acm.org/doi/abs/10.1145/3786582.3786809</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0245</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Metamorphic Fairness Testing of Retrieval-Augmented Generation: Diagnosing Retriever Bias and Evaluating Graph-based Mitigation</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://journals-sol.sbc.org.br/index.php/jserd/article/view/7713</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0247</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Testing JSON Schema Instruction Artifacts: Distributional Robustness under Validation-Equivalent Serialization and JSON Mode</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://www.researchsquare.com/article/rs-10610100/latest</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>MU-0249</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>Uncovering Discriminatory Behavior in LLM-Based CV Screening Systems with Composite Statistical Metamorphic Relations</ns0:t>
+  </ns0:si>
+  <ns0:si>
+    <ns0:t>https://ijcai-preprints.s3.us-west-1.amazonaws.com/2026/HC39.pdf</ns0:t>
+  </ns0:si>
+</ns0:sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2572,7 +2572,7 @@
         <v>3</v>
       </c>
       <c r="B6" s="12">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7" ht="33" customHeight="1" spans="1:2">
@@ -2590,7 +2590,7 @@
       </c>
       <c r="B8" s="14">
         <f>B6-B7</f>
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1" spans="1:2">
